--- a/Termination_Liability_Config.xlsx
+++ b/Termination_Liability_Config.xlsx
@@ -668,7 +668,7 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>https://sanjkris.github.io/termination-liability-config/</t>
+          <t>https://sanjanakrishnam-rippling.github.io/termination-liability-config/</t>
         </is>
       </c>
     </row>

--- a/Termination_Liability_Config.xlsx
+++ b/Termination_Liability_Config.xlsx
@@ -2069,7 +2069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D151"/>
+  <dimension ref="A1:D163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2108,6 +2108,11 @@
           <t>Philippines (PH)</t>
         </is>
       </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Enter country name and code, e.g., 'Germany (DE)'</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
@@ -2132,183 +2137,205 @@
           <t>Entity Type</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>All</t>
         </is>
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>Only for DE, FR, BE — leave N/A otherwise</t>
+          <t>Only for applicable countries like DE, FR — Leave as All if it does not apply</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
+          <t>Province</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>Only applicable for countries with different rules per province — Leave as All if it does not apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
           <t>Is MTA the default practice?</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>No / Yes — always / Yes — above tenure threshold</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>2. Severance Cost Components</t>
-        </is>
-      </c>
-    </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Component 1: Redundancy Pay (default)</t>
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>2. MTA Configuration</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>Prorate for partial years?</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>Yes (default) / No — e.g., 30 days/yr with 8 months: Yes → 20 days, No → 0 days</t>
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>Fill only if Is MTA the default practice = 'Yes — always' OR 'Yes — above tenure threshold'</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>From (tenure months)</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>To (tenure months)</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>Method</t>
-        </is>
-      </c>
-      <c r="D12" s="14" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="B13" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="C13" s="15" t="inlineStr">
-        <is>
-          <t>Fixed</t>
-        </is>
-      </c>
-      <c r="D13" s="15" t="inlineStr">
-        <is>
-          <t>0 days</t>
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>How many days does it take to secure an MTA, on average? (excl. notice period days)</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr"/>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Days</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="B14" s="15" t="inlineStr">
-        <is>
-          <t>No limit</t>
-        </is>
-      </c>
-      <c r="C14" s="15" t="inlineStr">
-        <is>
-          <t>Per year of service</t>
-        </is>
-      </c>
-      <c r="D14" s="15" t="inlineStr">
-        <is>
-          <t>30 days per year of service</t>
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>How many days of severance are offered in exchange for the MTA signature?</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>Max cap (days)</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>None</t>
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>Fill the tier table below and max cap. Use 'No Limit' if the tenure range has no upper limit.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
+          <t>If severance days remain the same within a range, use Fixed. If they vary by years of service, use Per Year of Service.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>Prorate for partial years?</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>Yes (default) / No — e.g., 30 days/yr with 8 months: Yes → 20 days, No → 0 days</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>From (tenure months)</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>To (tenure months)</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>No Limit</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
           <t>↳ Add more tiers by inserting rows above this line</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>↳ To add another component, copy a component block above and change the label</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>3. MTA Configuration (if MTA = Yes)</t>
-        </is>
-      </c>
-    </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
-          <t>N/A — MTA is not the default for this country</t>
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>Max Cap</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Days</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>Fill if there is a maximum cap we need to adhere to</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>4. Vacation Payout</t>
+          <t>3. Severance Cost Components</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="13" t="inlineStr">
-        <is>
-          <t>For deposit sizing, we use the statutory entitlement from the EA/config — not the T&amp;A system balance (which HR does not trust).</t>
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Component 1: Redundancy Pay (default)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>Pay out accrued vacation during termination?</t>
+          <t>Prorate for partial years?</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
@@ -2318,873 +2345,953 @@
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
-          <t>Yes / No</t>
+          <t>Example: The policy grants 30 days of severance per year. If proration is applied, an employee with 8 months of tenure receives 20 days. If not applied, the employee receives 0 days.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>Statutory minimum payout type</t>
-        </is>
-      </c>
-      <c r="B26" s="12" t="inlineStr">
-        <is>
-          <t>All Accrued</t>
-        </is>
-      </c>
-      <c r="C26" s="13" t="inlineStr">
-        <is>
-          <t>All Accrued / Fixed number of days</t>
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>From (tenure months)</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>To (tenure months)</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="B27" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>0 days</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="13" t="inlineStr">
-        <is>
-          <t>For deposit sizing: we assume worst case = full annual entitlement from the EA (prorated to tenure). Actual usage is unknown at estimation time.</t>
+      <c r="A28" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>No limit</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>Per year of service</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>30 days per year of service</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>↳ Add more tiers by inserting rows above this line</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>5. Compensation Variable Metadata</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="13" t="inlineStr">
-        <is>
-          <t>For each compensation variable, indicate Yes/No for each column. New variables default to No.</t>
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>Max Cap</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Days</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>Fill if there is a maximum cap we need to adhere to</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="14" t="inlineStr">
-        <is>
-          <t>Compensation Variable</t>
-        </is>
-      </c>
-      <c r="B32" s="14" t="inlineStr">
-        <is>
-          <t>Included in Working Notice?</t>
-        </is>
-      </c>
-      <c r="C32" s="14" t="inlineStr">
-        <is>
-          <t>Included in Severance?</t>
-        </is>
-      </c>
-      <c r="D32" s="14" t="inlineStr">
-        <is>
-          <t>Included in Vacation Pay?</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="11" t="inlineStr">
-        <is>
-          <t>Gross Base Salary</t>
-        </is>
-      </c>
-      <c r="B33" s="15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C33" s="15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D33" s="15" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>↳ To add another component, copy a component block above and change the label</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="11" t="inlineStr">
-        <is>
-          <t>Target Bonus</t>
-        </is>
-      </c>
-      <c r="B34" s="15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C34" s="15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D34" s="15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="11" t="inlineStr">
-        <is>
-          <t>Signing Bonus</t>
-        </is>
-      </c>
-      <c r="B35" s="15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C35" s="15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D35" s="15" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>4. Vacation Payout</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>On-Target Commission</t>
-        </is>
-      </c>
-      <c r="B36" s="15" t="inlineStr">
+          <t>Pay out accrued vacation during termination?</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="C36" s="15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D36" s="15" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>Yes / No</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>Rice Allowance</t>
-        </is>
-      </c>
-      <c r="B37" s="15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C37" s="15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D37" s="15" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>What is the minimum that needs to be paid out?</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>All Accrued</t>
+        </is>
+      </c>
+      <c r="C37" s="13" t="inlineStr">
+        <is>
+          <t>Fill the tier table below and max cap if choosing "Fixed Number of Days"; Ignore if it is "All Accrued"</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="11" t="inlineStr">
-        <is>
-          <t>Uniform &amp; Clothing Allowance</t>
-        </is>
-      </c>
-      <c r="B38" s="15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C38" s="15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D38" s="15" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="A38" s="14" t="inlineStr">
+        <is>
+          <t>From (tenure months)</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>To (tenure months)</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="D38" s="14" t="inlineStr">
+        <is>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="11" t="inlineStr">
-        <is>
-          <t>Laundry Allowance</t>
-        </is>
-      </c>
-      <c r="B39" s="15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C39" s="15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D39" s="15" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="A39" s="13" t="inlineStr">
+        <is>
+          <t>↳ Add more tiers by inserting rows above this line</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t>Medical Cash Allowance</t>
-        </is>
-      </c>
-      <c r="B40" s="15" t="inlineStr">
+          <t>Max Cap</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Days</t>
+        </is>
+      </c>
+      <c r="D40" s="13" t="inlineStr">
+        <is>
+          <t>Fill if there is a maximum cap we need to adhere to</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>5. Compensation Variable Metadata</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="14" t="inlineStr">
+        <is>
+          <t>Compensation Variable</t>
+        </is>
+      </c>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>Included in Working Notice?</t>
+        </is>
+      </c>
+      <c r="C44" s="14" t="inlineStr">
+        <is>
+          <t>Included in Severance?</t>
+        </is>
+      </c>
+      <c r="D44" s="14" t="inlineStr">
+        <is>
+          <t>Included in Vacation Pay?</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>Gross Base Salary</t>
+        </is>
+      </c>
+      <c r="B45" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="C40" s="15" t="inlineStr">
+      <c r="C45" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D45" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>Target Bonus</t>
+        </is>
+      </c>
+      <c r="B46" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C46" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="D40" s="15" t="inlineStr">
+      <c r="D46" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="11" t="inlineStr">
-        <is>
-          <t>Internet Allowance</t>
-        </is>
-      </c>
-      <c r="B41" s="15" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t>Signing Bonus</t>
+        </is>
+      </c>
+      <c r="B47" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="C41" s="15" t="inlineStr">
+      <c r="C47" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="D41" s="15" t="inlineStr">
+      <c r="D47" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="11" t="inlineStr">
-        <is>
-          <t>Productivity Incentive Allowance</t>
-        </is>
-      </c>
-      <c r="B42" s="15" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t>On-Target Commission</t>
+        </is>
+      </c>
+      <c r="B48" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="C42" s="15" t="inlineStr">
+      <c r="C48" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="D42" s="15" t="inlineStr">
+      <c r="D48" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="11" t="inlineStr">
-        <is>
-          <t>Christmas / Anniversary Gift</t>
-        </is>
-      </c>
-      <c r="B43" s="15" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t>Rice Allowance</t>
+        </is>
+      </c>
+      <c r="B49" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="C43" s="15" t="inlineStr">
+      <c r="C49" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="D43" s="15" t="inlineStr">
+      <c r="D49" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="11" t="inlineStr">
-        <is>
-          <t>13th Month Salary</t>
-        </is>
-      </c>
-      <c r="B44" s="15" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="11" t="inlineStr">
+        <is>
+          <t>Uniform &amp; Clothing Allowance</t>
+        </is>
+      </c>
+      <c r="B50" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="C44" s="15" t="inlineStr">
+      <c r="C50" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="D44" s="15" t="inlineStr">
+      <c r="D50" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="13" t="inlineStr">
-        <is>
-          <t>↳ Add more variables by inserting rows above</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>6. Worked Examples — How Severance &amp; Vacation Pay Are Calculated</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="13" t="inlineStr">
-        <is>
-          <t>These examples show how the config above translates into actual severance days and dollar amounts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>Example 1: Employee with 3 months tenure (below 6-month threshold — no severance)</t>
-        </is>
-      </c>
-    </row>
     <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>Employee Profile</t>
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>Laundry Allowance</t>
+        </is>
+      </c>
+      <c r="B51" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C51" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D51" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Tenure</t>
-        </is>
-      </c>
-      <c r="B52" s="16" t="inlineStr">
-        <is>
-          <t>3 months</t>
+          <t>Medical Cash Allowance</t>
+        </is>
+      </c>
+      <c r="B52" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C52" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D52" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Gross Base Salary</t>
-        </is>
-      </c>
-      <c r="B53" s="16" t="inlineStr">
-        <is>
-          <t>₱80,000 / month</t>
+          <t>Internet Allowance</t>
+        </is>
+      </c>
+      <c r="B53" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C53" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D53" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
         <is>
+          <t>Productivity Incentive Allowance</t>
+        </is>
+      </c>
+      <c r="B54" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C54" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D54" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="11" t="inlineStr">
+        <is>
+          <t>Christmas / Anniversary Gift</t>
+        </is>
+      </c>
+      <c r="B55" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C55" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D55" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="11" t="inlineStr">
+        <is>
+          <t>13th Month Salary</t>
+        </is>
+      </c>
+      <c r="B56" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C56" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D56" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="13" t="inlineStr">
+        <is>
+          <t>↳ Add more variables by inserting rows above</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>6. Worked Examples — How Severance &amp; Vacation Pay Are Calculated</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="13" t="inlineStr">
+        <is>
+          <t>These examples show how the config above translates into actual severance days and dollar amounts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>Example 1: Employee with 3 months tenure (below 6-month threshold — no severance)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>Employee Profile</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Tenure</t>
+        </is>
+      </c>
+      <c r="B64" s="16" t="inlineStr">
+        <is>
+          <t>3 months</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Gross Base Salary</t>
+        </is>
+      </c>
+      <c r="B65" s="16" t="inlineStr">
+        <is>
+          <t>₱80,000 / month</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Accrued Vacation Balance</t>
         </is>
       </c>
-      <c r="B54" s="16" t="inlineStr">
+      <c r="B66" s="16" t="inlineStr">
         <is>
           <t>3 days</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
         <is>
           <t>Severance Calculation</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Step 1: Identify the matching tier for tenure = 3 months</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Tier 1: 0 → 6 months, Method: Fixed, Value: 0 days</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Employee is within the first 6 months → no severance entitlement</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="17" t="inlineStr">
-        <is>
-          <t>→ severance_days = 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>Vacation Payout Calculation</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Config says: All Accrued</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Employee has 3 days accrued</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="17" t="inlineStr">
-        <is>
-          <t>→ vacation_days_payout = 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>What Gets Passed to Risk</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  severance_days = 0 (below 6-month threshold)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  vacation_days_payout = 3</t>
+          <t xml:space="preserve">  Step 1: Identify the matching tier for tenure = 3 months</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="17" t="inlineStr">
-        <is>
-          <t>→ Passed to Risk for deposit calculation</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="4" t="inlineStr">
-        <is>
-          <t>Example 2: Employee with 8 months tenure (above threshold — prorated severance)</t>
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Tier 1: 0 → 6 months, Method: Fixed, Value: 0 days</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Employee is within the first 6 months → no severance entitlement</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="17" t="inlineStr">
+        <is>
+          <t>→ severance_days = 0</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>Employee Profile</t>
+          <t>Vacation Payout Calculation</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Tenure</t>
-        </is>
-      </c>
-      <c r="B75" s="16" t="inlineStr">
-        <is>
-          <t>8 months (0.67 years)</t>
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Config says: All Accrued</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Gross Base Salary</t>
-        </is>
-      </c>
-      <c r="B76" s="16" t="inlineStr">
-        <is>
-          <t>₱80,000 / month</t>
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Employee has 3 days accrued</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Accrued Vacation Balance</t>
-        </is>
-      </c>
-      <c r="B77" s="16" t="inlineStr">
-        <is>
-          <t>5 days</t>
+      <c r="A77" s="17" t="inlineStr">
+        <is>
+          <t>→ vacation_days_payout = 3</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>Severance Calculation</t>
+          <t>What Gets Passed to Risk</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Step 1: Identify the matching tier for tenure = 8 months</t>
+          <t xml:space="preserve">  severance_days = 0 (below 6-month threshold)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Tier 2: 6 → No limit months, Method: Per year of service, Value: 30 days/yr</t>
+          <t xml:space="preserve">  vacation_days_payout = 3</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Step 2: Calculate severance days (prorated)</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Tenure = 8 months = 8/12 years = 0.67 years</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    30 days/yr × 0.67 years = 20 days</t>
+      <c r="A82" s="17" t="inlineStr">
+        <is>
+          <t>→ Passed to Risk for deposit calculation</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Step 3: Check max cap → None</t>
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>Example 2: Employee with 8 months tenure (above threshold — prorated severance)</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="17" t="inlineStr">
-        <is>
-          <t>→ severance_days = 20</t>
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>Employee Profile</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="3" t="inlineStr">
-        <is>
-          <t>  </t>
+      <c r="A87" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Tenure</t>
+        </is>
+      </c>
+      <c r="B87" s="16" t="inlineStr">
+        <is>
+          <t>8 months (0.67 years)</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Proration breakdown for reference:</t>
+      <c r="A88" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Gross Base Salary</t>
+        </is>
+      </c>
+      <c r="B88" s="16" t="inlineStr">
+        <is>
+          <t>₱80,000 / month</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    At 6 months: 30 × (6/12) = 15 days</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    At 7 months: 30 × (7/12) = 17.5 days</t>
+      <c r="A89" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Accrued Vacation Balance</t>
+        </is>
+      </c>
+      <c r="B89" s="16" t="inlineStr">
+        <is>
+          <t>5 days</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    At 8 months: 30 × (8/12) = 20 days</t>
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>Severance Calculation</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    At 12 months: 30 × (12/12) = 30 days</t>
+          <t xml:space="preserve">  Step 1: Identify the matching tier for tenure = 8 months</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Tier 2: 6 → No limit months, Method: Per year of service, Value: 30 days/yr</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="5" t="inlineStr">
-        <is>
-          <t>Vacation Payout Calculation</t>
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Step 2: Calculate severance days (prorated)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Config says: All Accrued</t>
+          <t xml:space="preserve">    Tenure = 8 months = 8/12 years = 0.67 years</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Employee has 5 days accrued</t>
+          <t xml:space="preserve">    30 days/yr × 0.67 years = 20 days</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="17" t="inlineStr">
-        <is>
-          <t>→ vacation_days_payout = 5</t>
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Step 3: Check max cap → None</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="17" t="inlineStr">
+        <is>
+          <t>→ severance_days = 20</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="5" t="inlineStr">
-        <is>
-          <t>What Gets Passed to Risk</t>
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>  </t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  severance_days = 20 (prorated for 8 months)</t>
+          <t xml:space="preserve">  Proration breakdown for reference:</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  vacation_days_payout = 5</t>
+          <t xml:space="preserve">    At 6 months: 30 × (6/12) = 15 days</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="17" t="inlineStr">
-        <is>
-          <t>→ Passed to Risk for deposit calculation</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="4" t="inlineStr">
-        <is>
-          <t>Example 3: Employee with 2.5 years tenure (full proration)</t>
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    At 7 months: 30 × (7/12) = 17.5 days</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    At 8 months: 30 × (8/12) = 20 days</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    At 12 months: 30 × (12/12) = 30 days</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>Employee Profile</t>
+          <t>Vacation Payout Calculation</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Tenure</t>
-        </is>
-      </c>
-      <c r="B107" s="16" t="inlineStr">
-        <is>
-          <t>2 years, 6 months (2.5 years)</t>
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Config says: All Accrued</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Gross Base Salary</t>
-        </is>
-      </c>
-      <c r="B108" s="16" t="inlineStr">
-        <is>
-          <t>₱100,000 / month</t>
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Employee has 5 days accrued</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Accrued Vacation Balance</t>
-        </is>
-      </c>
-      <c r="B109" s="16" t="inlineStr">
-        <is>
-          <t>18 days</t>
+      <c r="A109" s="17" t="inlineStr">
+        <is>
+          <t>→ vacation_days_payout = 5</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>Severance Calculation</t>
+          <t>What Gets Passed to Risk</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Step 1: Identify the matching tier for tenure = 30 months</t>
+          <t xml:space="preserve">  severance_days = 20 (prorated for 8 months)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">  vacation_days_payout = 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="17" t="inlineStr">
+        <is>
+          <t>→ Passed to Risk for deposit calculation</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>Example 3: Employee with 2.5 years tenure (full proration)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>Employee Profile</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Tenure</t>
+        </is>
+      </c>
+      <c r="B119" s="16" t="inlineStr">
+        <is>
+          <t>2 years, 6 months (2.5 years)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Gross Base Salary</t>
+        </is>
+      </c>
+      <c r="B120" s="16" t="inlineStr">
+        <is>
+          <t>₱100,000 / month</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Accrued Vacation Balance</t>
+        </is>
+      </c>
+      <c r="B121" s="16" t="inlineStr">
+        <is>
+          <t>18 days</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>Severance Calculation</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Step 1: Identify the matching tier for tenure = 30 months</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">    Tier 2: 6 → No limit months, Method: Per year of service, Value: 30 days/yr</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="3" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">  Step 2: Calculate severance days (prorated)</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Tenure = 2.5 years × 30 days/yr = 75 days</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Step 3: Check max cap → None</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="17" t="inlineStr">
-        <is>
-          <t>→ severance_days = 75</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="3" t="inlineStr">
-        <is>
-          <t>  </t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Step 4: Determine severance salary basis (comp vars where Severance = Yes)</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Only 'Gross Base Salary' is included in severance</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Severance daily rate = ₱100,000 / 30 = ₱3,333.33</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Step 5: Calculate severance pay</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  = 75 days × ₱3,333.33 = ₱250,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="17" t="inlineStr">
-        <is>
-          <t>→ Severance pay = ₱250,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="5" t="inlineStr">
-        <is>
-          <t>Vacation Payout Calculation</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Config says: All Accrued</t>
+          <t xml:space="preserve">    Tenure = 2.5 years × 30 days/yr = 75 days</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Employee has 18 days accrued</t>
+          <t xml:space="preserve">  Step 3: Check max cap → None</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="17" t="inlineStr">
         <is>
-          <t>→ vacation_days_payout = 18</t>
+          <t>→ severance_days = 75</t>
         </is>
       </c>
     </row>
@@ -3198,251 +3305,334 @@
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Vacation pay salary basis (comp vars where Vacation Pay = Yes):</t>
+          <t xml:space="preserve">  Step 4: Determine severance salary basis (comp vars where Severance = Yes)</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Only 'Gross Base Salary' is included</t>
+          <t xml:space="preserve">    Only 'Gross Base Salary' is included in severance</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Vacation daily rate = ₱100,000 / 30 = ₱3,333.33</t>
+          <t xml:space="preserve">    Severance daily rate = ₱100,000 / 30 = ₱3,333.33</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  = 18 days × ₱3,333.33 = ₱60,000</t>
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Step 5: Calculate severance pay</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="17" t="inlineStr">
-        <is>
-          <t>→ Vacation payout = ₱60,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="5" t="inlineStr">
-        <is>
-          <t>What Gets Passed to Risk</t>
+      <c r="A135" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  = 75 days × ₱3,333.33 = ₱250,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="17" t="inlineStr">
+        <is>
+          <t>→ Severance pay = ₱250,000</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  severance_days = 75 (passed to Risk)</t>
+      <c r="A138" s="5" t="inlineStr">
+        <is>
+          <t>Vacation Payout Calculation</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  vacation_days_payout = 18 (passed to Risk)</t>
+          <t xml:space="preserve">  Config says: All Accrued</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="17" t="inlineStr">
-        <is>
-          <t>→ Risk uses the salary bases above to convert days → dollar amounts for deposit sizing</t>
+      <c r="A140" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Employee has 18 days accrued</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="17" t="inlineStr">
+        <is>
+          <t>→ vacation_days_payout = 18</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>  </t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="13" t="inlineStr">
-        <is>
-          <t>Note: Risk converts severance_days into a dollar amount using the severance salary basis (comp variables marked 'Included in Severance = Yes').</t>
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Vacation pay salary basis (comp vars where Vacation Pay = Yes):</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="13" t="inlineStr">
-        <is>
-          <t>Note: Risk converts vacation_days_payout into a dollar amount using the vacation pay salary basis (comp variables marked 'Included in Vacation Pay = Yes').</t>
+      <c r="A144" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Only 'Gross Base Salary' is included</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Vacation daily rate = ₱100,000 / 30 = ₱3,333.33</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="4" t="inlineStr">
-        <is>
-          <t>7. Notes / Items Not Captured</t>
+      <c r="A146" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  = 18 days × ₱3,333.33 = ₱60,000</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="13" t="inlineStr">
-        <is>
-          <t>Use this section to flag anything the config above cannot express:</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="3" t="inlineStr">
-        <is>
-          <t>• 0–6 months tenure: no severance entitlement.</t>
+      <c r="A147" s="17" t="inlineStr">
+        <is>
+          <t>→ Vacation payout = ₱60,000</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="3" t="inlineStr">
-        <is>
-          <t>• 6 months and above: 30 days per year of service, prorated for partial years.</t>
+      <c r="A149" s="5" t="inlineStr">
+        <is>
+          <t>What Gets Passed to Risk</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>• In PH, full compensation is paid during notice period, but severance uses base salary only.</t>
+          <t xml:space="preserve">  severance_days = 75 (passed to Risk)</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">  vacation_days_payout = 18 (passed to Risk)</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="17" t="inlineStr">
+        <is>
+          <t>→ Risk uses the salary bases above to convert days → dollar amounts for deposit sizing</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="13" t="inlineStr">
+        <is>
+          <t>Note: Risk converts severance_days into a dollar amount using the severance salary basis (comp variables marked 'Included in Severance = Yes').</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="13" t="inlineStr">
+        <is>
+          <t>Note: Risk converts vacation_days_payout into a dollar amount using the vacation pay salary basis (comp variables marked 'Included in Vacation Pay = Yes').</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="4" t="inlineStr">
+        <is>
+          <t>7. Notes / Items Not Captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="13" t="inlineStr">
+        <is>
+          <t>Use this section to flag anything the config above cannot express:</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="inlineStr">
+        <is>
+          <t>• 0–6 months tenure: no severance entitlement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="inlineStr">
+        <is>
+          <t>• 6 months and above: 30 days per year of service, prorated for partial years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="inlineStr">
+        <is>
+          <t>• In PH, full compensation is paid during notice period, but severance uses base salary only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="inlineStr">
+        <is>
           <t>• 13th Month Salary is mandatory and always included in working notice.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="43">
+  <dataValidations count="45">
     <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
       <formula1>"Indefinite,Fixed Term"</formula1>
     </dataValidation>
-    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
       <formula1>"No,Yes — always,Yes — above tenure threshold"</formula1>
     </dataValidation>
-    <dataValidation sqref="B11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+    <dataValidation sqref="B17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
       <formula1>"Fixed,Per year of service"</formula1>
     </dataValidation>
-    <dataValidation sqref="C14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+    <dataValidation sqref="B25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
       <formula1>"Fixed,Per year of service"</formula1>
     </dataValidation>
-    <dataValidation sqref="B25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+    <dataValidation sqref="C28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Fixed,Per year of service"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
       <formula1>"All Accrued,Fixed number of days"</formula1>
     </dataValidation>
-    <dataValidation sqref="B33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+    <dataValidation sqref="B45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B55" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C55" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D55" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3457,7 +3647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D141"/>
+  <dimension ref="A1:D153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3496,6 +3686,11 @@
           <t>Spain (ES)</t>
         </is>
       </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Enter country name and code, e.g., 'Germany (DE)'</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
@@ -3520,902 +3715,997 @@
           <t>Entity Type</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>All</t>
         </is>
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>Only for DE, FR, BE — leave N/A otherwise</t>
+          <t>Only for applicable countries like DE, FR — Leave as All if it does not apply</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
+          <t>Province</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>Only applicable for countries with different rules per province — Leave as All if it does not apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
           <t>Is MTA the default practice?</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>No / Yes — always / Yes — above tenure threshold</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>2. Severance Cost Components</t>
-        </is>
-      </c>
-    </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Component 1: Severance — Objective Dismissal (Procedente) (default)</t>
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>2. MTA Configuration</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>Prorate for partial years?</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>Yes (default) / No — e.g., 30 days/yr with 8 months: Yes → 20 days, No → 0 days</t>
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>Fill only if Is MTA the default practice = 'Yes — always' OR 'Yes — above tenure threshold'</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>From (tenure months)</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>To (tenure months)</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>Method</t>
-        </is>
-      </c>
-      <c r="D12" s="14" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>No limit</t>
-        </is>
-      </c>
-      <c r="C13" s="15" t="inlineStr">
-        <is>
-          <t>Per year of service</t>
-        </is>
-      </c>
-      <c r="D13" s="15" t="inlineStr">
-        <is>
-          <t>20 days per year of service</t>
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>How many days does it take to secure an MTA, on average? (excl. notice period days)</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr"/>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Days</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>Max cap (days)</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>360</t>
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>How many days of severance are offered in exchange for the MTA signature?</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>↳ Add more tiers by inserting rows above this line</t>
+          <t>Fill the tier table below and max cap. Use 'No Limit' if the tenure range has no upper limit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>If severance days remain the same within a range, use Fixed. If they vary by years of service, use Per Year of Service.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
-        <is>
-          <t>↳ To add another component, copy a component block above and change the label</t>
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>Prorate for partial years?</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>Yes (default) / No — e.g., 30 days/yr with 8 months: Yes → 20 days, No → 0 days</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>From (tenure months)</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>To (tenure months)</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>3. MTA Configuration (if MTA = Yes)</t>
+      <c r="A19" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>No Limit</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>N/A — MTA is not the default for this country</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>4. Vacation Payout</t>
+          <t>↳ Add more tiers by inserting rows above this line</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>Max Cap</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Days</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>Fill if there is a maximum cap we need to adhere to</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="13" t="inlineStr">
-        <is>
-          <t>For deposit sizing, we use the statutory entitlement from the EA/config — not the T&amp;A system balance (which HR does not trust).</t>
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>3. Severance Cost Components</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>Pay out accrued vacation during termination?</t>
-        </is>
-      </c>
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C24" s="13" t="inlineStr">
-        <is>
-          <t>Yes / No</t>
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Component 1: Severance — Objective Dismissal (Procedente) (default)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>Statutory minimum payout type</t>
+          <t>Prorate for partial years?</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>All Accrued</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
-          <t>All Accrued / Fixed number of days</t>
+          <t>Example: The policy grants 30 days of severance per year. If proration is applied, an employee with 8 months of tenure receives 20 days. If not applied, the employee receives 0 days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>From (tenure months)</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>To (tenure months)</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="inlineStr">
-        <is>
-          <t>For deposit sizing: we assume worst case = full annual entitlement from the EA (prorated to tenure). Actual usage is unknown at estimation time.</t>
+      <c r="A27" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>No limit</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>Per year of service</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>20 days per year of service</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>↳ Add more tiers by inserting rows above this line</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>5. Compensation Variable Metadata</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="13" t="inlineStr">
-        <is>
-          <t>For each compensation variable, indicate Yes/No for each column. New variables default to No.</t>
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>Max Cap</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Days</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>Fill if there is a maximum cap we need to adhere to</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="14" t="inlineStr">
-        <is>
-          <t>Compensation Variable</t>
-        </is>
-      </c>
-      <c r="B31" s="14" t="inlineStr">
-        <is>
-          <t>Included in Working Notice?</t>
-        </is>
-      </c>
-      <c r="C31" s="14" t="inlineStr">
-        <is>
-          <t>Included in Severance?</t>
-        </is>
-      </c>
-      <c r="D31" s="14" t="inlineStr">
-        <is>
-          <t>Included in Vacation Pay?</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="11" t="inlineStr">
-        <is>
-          <t>Gross Base Salary</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C32" s="15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D32" s="15" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>↳ To add another component, copy a component block above and change the label</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="inlineStr">
-        <is>
-          <t>Pagas Extra (13th/14th Month)</t>
-        </is>
-      </c>
-      <c r="B33" s="15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C33" s="15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D33" s="15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="11" t="inlineStr">
-        <is>
-          <t>Target Bonus</t>
-        </is>
-      </c>
-      <c r="B34" s="15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C34" s="15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D34" s="15" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>4. Vacation Payout</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>On-Target Commission</t>
-        </is>
-      </c>
-      <c r="B35" s="15" t="inlineStr">
+          <t>Pay out accrued vacation during termination?</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="C35" s="15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D35" s="15" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>Yes / No</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>Meal Allowance</t>
-        </is>
-      </c>
-      <c r="B36" s="15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C36" s="15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D36" s="15" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>What is the minimum that needs to be paid out?</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>All Accrued</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>Fill the tier table below and max cap if choosing "Fixed Number of Days"; Ignore if it is "All Accrued"</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="11" t="inlineStr">
-        <is>
-          <t>Transport Allowance</t>
-        </is>
-      </c>
-      <c r="B37" s="15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C37" s="15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D37" s="15" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="A37" s="14" t="inlineStr">
+        <is>
+          <t>From (tenure months)</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>To (tenure months)</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="D37" s="14" t="inlineStr">
+        <is>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>↳ Add more variables by inserting rows above</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>6. Worked Examples — How Severance &amp; Vacation Pay Are Calculated</t>
+          <t>↳ Add more tiers by inserting rows above this line</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>Max Cap</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Days</t>
+        </is>
+      </c>
+      <c r="D39" s="13" t="inlineStr">
+        <is>
+          <t>Fill if there is a maximum cap we need to adhere to</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="13" t="inlineStr">
-        <is>
-          <t>These examples show how the config above translates into actual severance days and dollar amounts.</t>
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>5. Compensation Variable Metadata</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>Example 1: Employee with 5 years tenure — Objective Dismissal</t>
+      <c r="A43" s="14" t="inlineStr">
+        <is>
+          <t>Compensation Variable</t>
+        </is>
+      </c>
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>Included in Working Notice?</t>
+        </is>
+      </c>
+      <c r="C43" s="14" t="inlineStr">
+        <is>
+          <t>Included in Severance?</t>
+        </is>
+      </c>
+      <c r="D43" s="14" t="inlineStr">
+        <is>
+          <t>Included in Vacation Pay?</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>Employee Profile</t>
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>Gross Base Salary</t>
+        </is>
+      </c>
+      <c r="B44" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C44" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D44" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Tenure</t>
-        </is>
-      </c>
-      <c r="B45" s="16" t="inlineStr">
-        <is>
-          <t>5 years (60 months)</t>
+          <t>Pagas Extra (13th/14th Month)</t>
+        </is>
+      </c>
+      <c r="B45" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C45" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D45" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Gross Base Salary</t>
-        </is>
-      </c>
-      <c r="B46" s="16" t="inlineStr">
-        <is>
-          <t>€4,000 / month</t>
+          <t>Target Bonus</t>
+        </is>
+      </c>
+      <c r="B46" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C46" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D46" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Pagas Extra (13th/14th)</t>
-        </is>
-      </c>
-      <c r="B47" s="16" t="inlineStr">
-        <is>
-          <t>€8,000 / year (= €666.67 / month equivalent)</t>
+          <t>On-Target Commission</t>
+        </is>
+      </c>
+      <c r="B47" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C47" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D47" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Target Bonus</t>
-        </is>
-      </c>
-      <c r="B48" s="16" t="inlineStr">
-        <is>
-          <t>€6,000 / year</t>
+          <t>Meal Allowance</t>
+        </is>
+      </c>
+      <c r="B48" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C48" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D48" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
         <is>
+          <t>Transport Allowance</t>
+        </is>
+      </c>
+      <c r="B49" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C49" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D49" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="13" t="inlineStr">
+        <is>
+          <t>↳ Add more variables by inserting rows above</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>6. Worked Examples — How Severance &amp; Vacation Pay Are Calculated</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="13" t="inlineStr">
+        <is>
+          <t>These examples show how the config above translates into actual severance days and dollar amounts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Example 1: Employee with 5 years tenure — Objective Dismissal</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>Employee Profile</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Tenure</t>
+        </is>
+      </c>
+      <c r="B57" s="16" t="inlineStr">
+        <is>
+          <t>5 years (60 months)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Gross Base Salary</t>
+        </is>
+      </c>
+      <c r="B58" s="16" t="inlineStr">
+        <is>
+          <t>€4,000 / month</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Pagas Extra (13th/14th)</t>
+        </is>
+      </c>
+      <c r="B59" s="16" t="inlineStr">
+        <is>
+          <t>€8,000 / year (= €666.67 / month equivalent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Target Bonus</t>
+        </is>
+      </c>
+      <c r="B60" s="16" t="inlineStr">
+        <is>
+          <t>€6,000 / year</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Accrued Vacation Balance</t>
         </is>
       </c>
-      <c r="B49" s="16" t="inlineStr">
+      <c r="B61" s="16" t="inlineStr">
         <is>
           <t>12 days</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
         <is>
           <t>Severance Calculation</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Step 1: Identify the component → Objective Dismissal</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Tier: 0 → No limit months, Method: Per year of service, Value: 20 days/yr</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>  </t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Step 2: Calculate severance days</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Tenure = 5 years × 20 days/yr = 100 days</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>  </t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Step 3: Check max cap</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Max cap = 360 days → 100 &lt; 360, no cap applies</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="17" t="inlineStr">
-        <is>
-          <t>→ severance_days = 100</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>  </t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Step 4: Determine severance salary basis (comp vars where Severance = Yes)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Gross Base Salary: €4,000/month ✓</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Pagas Extra: €666.67/month ✓</t>
+          <t xml:space="preserve">  Step 1: Identify the component → Objective Dismissal</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Target Bonus: ✗ (not in severance basis)</t>
+          <t xml:space="preserve">    Tier: 0 → No limit months, Method: Per year of service, Value: 20 days/yr</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Total monthly severance basis = €4,666.67</t>
+          <t>  </t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Daily rate = €4,666.67 / 30 = €155.56</t>
+          <t xml:space="preserve">  Step 2: Calculate severance days</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>  </t>
+          <t xml:space="preserve">    Tenure = 5 years × 20 days/yr = 100 days</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Step 5: Calculate severance pay</t>
+          <t>  </t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  = 100 days × €155.56 = €15,556</t>
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Step 3: Check max cap</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="17" t="inlineStr">
-        <is>
-          <t>→ Severance pay = €15,556</t>
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Max cap = 360 days → 100 &lt; 360, no cap applies</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="17" t="inlineStr">
+        <is>
+          <t>→ severance_days = 100</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>Vacation Payout Calculation</t>
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>  </t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Config says: All Accrued</t>
+          <t xml:space="preserve">  Step 4: Determine severance salary basis (comp vars where Severance = Yes)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Employee has 12 days accrued</t>
+          <t xml:space="preserve">    Gross Base Salary: €4,000/month ✓</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="17" t="inlineStr">
-        <is>
-          <t>→ vacation_days_payout = 12</t>
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Pagas Extra: €666.67/month ✓</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>  </t>
+          <t xml:space="preserve">    Target Bonus: ✗ (not in severance basis)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Vacation pay salary basis (comp vars where Vacation Pay = Yes):</t>
+          <t xml:space="preserve">    Total monthly severance basis = €4,666.67</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Gross Base Salary: €4,000/month ✓</t>
+          <t xml:space="preserve">    Daily rate = €4,666.67 / 30 = €155.56</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Pagas Extra: €666.67/month ✓</t>
+          <t>  </t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Daily rate = €4,666.67 / 30 = €155.56</t>
+          <t xml:space="preserve">  Step 5: Calculate severance pay</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  = 12 days × €155.56 = €1,866.67</t>
+          <t xml:space="preserve">  = 100 days × €155.56 = €15,556</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="17" t="inlineStr">
         <is>
-          <t>→ Vacation payout = €1,866.67</t>
+          <t>→ Severance pay = €15,556</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>What Gets Passed to Risk</t>
+          <t>Vacation Payout Calculation</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  severance_days = 100 (passed to Risk)</t>
+          <t xml:space="preserve">  Config says: All Accrued</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  vacation_days_payout = 12 (passed to Risk)</t>
+          <t xml:space="preserve">  Employee has 12 days accrued</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="17" t="inlineStr">
         <is>
-          <t>→ Risk uses the salary bases to convert → total deposit exposure = €15,556 + €1,866.67 = €17,423</t>
+          <t>→ vacation_days_payout = 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>  </t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Vacation pay salary basis (comp vars where Vacation Pay = Yes):</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="4" t="inlineStr">
-        <is>
-          <t>Example 2: Employee with 20 years tenure — Cap applies</t>
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Gross Base Salary: €4,000/month ✓</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="5" t="inlineStr">
-        <is>
-          <t>Employee Profile</t>
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Pagas Extra: €666.67/month ✓</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Tenure</t>
-        </is>
-      </c>
-      <c r="B93" s="16" t="inlineStr">
-        <is>
-          <t>20 years (240 months)</t>
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Daily rate = €4,666.67 / 30 = €155.56</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Gross Base Salary</t>
-        </is>
-      </c>
-      <c r="B94" s="16" t="inlineStr">
-        <is>
-          <t>€5,000 / month</t>
+      <c r="A94" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  = 12 days × €155.56 = €1,866.67</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Pagas Extra (13th/14th)</t>
-        </is>
-      </c>
-      <c r="B95" s="16" t="inlineStr">
-        <is>
-          <t>€10,000 / year (= €833.33 / month equivalent)</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Accrued Vacation Balance</t>
-        </is>
-      </c>
-      <c r="B96" s="16" t="inlineStr">
-        <is>
-          <t>22 days</t>
+      <c r="A95" s="17" t="inlineStr">
+        <is>
+          <t>→ Vacation payout = €1,866.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>What Gets Passed to Risk</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="5" t="inlineStr">
-        <is>
-          <t>Severance Calculation</t>
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  severance_days = 100 (passed to Risk)</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Step 1: Identify the component → Objective Dismissal</t>
+          <t xml:space="preserve">  vacation_days_payout = 12 (passed to Risk)</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Tier: 0 → No limit months, Method: Per year of service, Value: 20 days/yr</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="3" t="inlineStr">
-        <is>
-          <t>  </t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Step 2: Calculate severance days (before cap)</t>
+      <c r="A100" s="17" t="inlineStr">
+        <is>
+          <t>→ Risk uses the salary bases to convert → total deposit exposure = €15,556 + €1,866.67 = €17,423</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Tenure = 20 years × 20 days/yr = 400 days</t>
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>Example 2: Employee with 20 years tenure — Cap applies</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="3" t="inlineStr">
-        <is>
-          <t>  </t>
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>Employee Profile</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Step 3: Check max cap</t>
+      <c r="A105" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Tenure</t>
+        </is>
+      </c>
+      <c r="B105" s="16" t="inlineStr">
+        <is>
+          <t>20 years (240 months)</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Max cap = 360 days → 400 &gt; 360, CAP APPLIES</t>
+      <c r="A106" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Gross Base Salary</t>
+        </is>
+      </c>
+      <c r="B106" s="16" t="inlineStr">
+        <is>
+          <t>€5,000 / month</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="17" t="inlineStr">
-        <is>
-          <t>→ severance_days = 360 (capped)</t>
+      <c r="A107" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Pagas Extra (13th/14th)</t>
+        </is>
+      </c>
+      <c r="B107" s="16" t="inlineStr">
+        <is>
+          <t>€10,000 / year (= €833.33 / month equivalent)</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="3" t="inlineStr">
-        <is>
-          <t>  </t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Step 4: Severance salary basis</t>
+      <c r="A108" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Accrued Vacation Balance</t>
+        </is>
+      </c>
+      <c r="B108" s="16" t="inlineStr">
+        <is>
+          <t>22 days</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Base + Pagas Extra = €5,000 + €833.33 = €5,833.33/month</t>
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>Severance Calculation</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Daily rate = €5,833.33 / 30 = €194.44</t>
+          <t xml:space="preserve">  Step 1: Identify the component → Objective Dismissal</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>  </t>
+          <t xml:space="preserve">    Tier: 0 → No limit months, Method: Per year of service, Value: 20 days/yr</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Step 5: Calculate severance pay</t>
+          <t>  </t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  = 360 days × €194.44 = €70,000</t>
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Step 2: Calculate severance days (before cap)</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="17" t="inlineStr">
-        <is>
-          <t>→ Severance pay = €70,000</t>
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Tenure = 20 years × 20 days/yr = 400 days</t>
         </is>
       </c>
     </row>
@@ -4429,215 +4719,305 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Without the cap it would have been 400 × €194.44 = €77,778 — the cap saves €7,778</t>
+          <t xml:space="preserve">  Step 3: Check max cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Max cap = 360 days → 400 &gt; 360, CAP APPLIES</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="5" t="inlineStr">
-        <is>
-          <t>Vacation Payout Calculation</t>
+      <c r="A119" s="17" t="inlineStr">
+        <is>
+          <t>→ severance_days = 360 (capped)</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Config says: All Accrued</t>
+          <t>  </t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Employee has 22 days accrued</t>
+          <t xml:space="preserve">  Step 4: Severance salary basis</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="17" t="inlineStr">
-        <is>
-          <t>→ vacation_days_payout = 22</t>
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Base + Pagas Extra = €5,000 + €833.33 = €5,833.33/month</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  = 22 × €194.44 = €4,278</t>
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Daily rate = €5,833.33 / 30 = €194.44</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="17" t="inlineStr">
-        <is>
-          <t>→ Vacation payout = €4,278</t>
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>  </t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Step 5: Calculate severance pay</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="5" t="inlineStr">
-        <is>
-          <t>What Gets Passed to Risk</t>
+      <c r="A126" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  = 360 days × €194.44 = €70,000</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  severance_days = 360 (capped from 400)</t>
+      <c r="A127" s="17" t="inlineStr">
+        <is>
+          <t>→ Severance pay = €70,000</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  vacation_days_payout = 22</t>
+          <t>  </t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="17" t="inlineStr">
-        <is>
-          <t>→ Total deposit exposure = €70,000 + €4,278 = €74,278</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="17" t="inlineStr">
-        <is>
-          <t>→ This demonstrates why the max cap matters — it prevents runaway liability for long-tenured employees</t>
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Without the cap it would have been 400 × €194.44 = €77,778 — the cap saves €7,778</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>Vacation Payout Calculation</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Config says: All Accrued</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="13" t="inlineStr">
-        <is>
-          <t>Note: Risk converts severance_days into a dollar amount using the severance salary basis (comp variables marked 'Included in Severance = Yes').</t>
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Employee has 22 days accrued</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="13" t="inlineStr">
-        <is>
-          <t>Note: Risk converts vacation_days_payout into a dollar amount using the vacation pay salary basis (comp variables marked 'Included in Vacation Pay = Yes').</t>
+      <c r="A134" s="17" t="inlineStr">
+        <is>
+          <t>→ vacation_days_payout = 22</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  = 22 × €194.44 = €4,278</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="4" t="inlineStr">
-        <is>
-          <t>7. Notes / Items Not Captured</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="13" t="inlineStr">
-        <is>
-          <t>Use this section to flag anything the config above cannot express:</t>
+      <c r="A136" s="17" t="inlineStr">
+        <is>
+          <t>→ Vacation payout = €4,278</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="3" t="inlineStr">
-        <is>
-          <t>• We model objective dismissal (20 days/yr, capped at 360 days) as the standard severance path. Unfair dismissal is rare and handled case by case.</t>
+      <c r="A138" s="5" t="inlineStr">
+        <is>
+          <t>What Gets Passed to Risk</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>• Pagas extra (extraordinary payments) are 2 extra monthly payments per year, typically paid in June and December. They are included in the severance salary basis.</t>
+          <t xml:space="preserve">  severance_days = 360 (capped from 400)</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">  vacation_days_payout = 22</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="17" t="inlineStr">
+        <is>
+          <t>→ Total deposit exposure = €70,000 + €4,278 = €74,278</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="17" t="inlineStr">
+        <is>
+          <t>→ This demonstrates why the max cap matters — it prevents runaway liability for long-tenured employees</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="13" t="inlineStr">
+        <is>
+          <t>Note: Risk converts severance_days into a dollar amount using the severance salary basis (comp variables marked 'Included in Severance = Yes').</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="13" t="inlineStr">
+        <is>
+          <t>Note: Risk converts vacation_days_payout into a dollar amount using the vacation pay salary basis (comp variables marked 'Included in Vacation Pay = Yes').</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="4" t="inlineStr">
+        <is>
+          <t>7. Notes / Items Not Captured</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="13" t="inlineStr">
+        <is>
+          <t>Use this section to flag anything the config above cannot express:</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="inlineStr">
+        <is>
+          <t>• We model objective dismissal (20 days/yr, capped at 360 days) as the standard severance path. Unfair dismissal is rare and handled case by case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>• Pagas extra (extraordinary payments) are 2 extra monthly payments per year, typically paid in June and December. They are included in the severance salary basis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="inlineStr">
+        <is>
           <t>• Prorated pagas extra must also be paid out at termination (final settlement / finiquito).</t>
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="3" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="3" t="inlineStr">
         <is>
           <t>• 15-day notice period required for objective dismissals. No notice required for disciplinary dismissals.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="24">
+  <dataValidations count="26">
     <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
       <formula1>"Indefinite,Fixed Term"</formula1>
     </dataValidation>
-    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
       <formula1>"No,Yes — always,Yes — above tenure threshold"</formula1>
     </dataValidation>
-    <dataValidation sqref="B11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+    <dataValidation sqref="B17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
       <formula1>"Fixed,Per year of service"</formula1>
     </dataValidation>
-    <dataValidation sqref="B24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
     <dataValidation sqref="B25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Fixed,Per year of service"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
       <formula1>"All Accrued,Fixed number of days"</formula1>
     </dataValidation>
-    <dataValidation sqref="B32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+    <dataValidation sqref="B44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4652,7 +5032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -4699,7 +5079,11 @@
           <t>Contract Type</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr"/>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Fixed Term</t>
+        </is>
+      </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
           <t>Indefinite / Fixed Term</t>
@@ -4712,337 +5096,673 @@
           <t>Entity Type</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>All</t>
         </is>
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>Only for DE, FR, BE — leave N/A otherwise</t>
+          <t>Only for applicable countries like DE, FR — Leave as All if it does not apply</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
+          <t>Province</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>Only applicable for countries with different rules per province — Leave as All if it does not apply</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
           <t>Is MTA the default practice?</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Yes — above tenure threshold</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>No / Yes — always / Yes — above tenure threshold</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>2. Severance Cost Components</t>
-        </is>
-      </c>
-    </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Component 1: Redundancy Pay (default)</t>
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>2. MTA Configuration</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>Prorate for partial years?</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>Yes (default) / No — e.g., 30 days/yr with 8 months: Yes → 20 days, No → 0 days</t>
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>Fill only if Is MTA the default practice = 'Yes — always' OR 'Yes — above tenure threshold'</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>From (tenure months)</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>To (tenure months)</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>Method</t>
-        </is>
-      </c>
-      <c r="D12" s="14" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="15" t="inlineStr"/>
-      <c r="B13" s="15" t="inlineStr"/>
-      <c r="C13" s="15" t="inlineStr"/>
-      <c r="D13" s="15" t="inlineStr"/>
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>How many days does it take to secure an MTA, on average? (excl. notice period days)</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr"/>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Days</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr"/>
-      <c r="B14" s="15" t="inlineStr"/>
-      <c r="C14" s="15" t="inlineStr"/>
-      <c r="D14" s="15" t="inlineStr"/>
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>How many days of severance are offered in exchange for the MTA signature?</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>Max cap (days)</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="inlineStr"/>
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>Fill the tier table below and max cap. Use 'No Limit' if the tenure range has no upper limit.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
+          <t>If severance days remain the same within a range, use Fixed. If they vary by years of service, use Per Year of Service.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>Prorate for partial years?</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>Yes (default) / No — e.g., 30 days/yr with 8 months: Yes → 20 days, No → 0 days</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>From (tenure months)</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>To (tenure months)</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>No Limit</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr"/>
+      <c r="B20" s="15" t="inlineStr"/>
+      <c r="C20" s="15" t="inlineStr"/>
+      <c r="D20" s="15" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr"/>
+      <c r="B21" s="15" t="inlineStr"/>
+      <c r="C21" s="15" t="inlineStr"/>
+      <c r="D21" s="15" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
           <t>↳ Add more tiers by inserting rows above this line</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>↳ To add another component, copy a component block above and change the label</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>3. MTA Configuration (if MTA = Yes)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
-          <t>N/A — MTA is not the default for this country</t>
-        </is>
-      </c>
-    </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>4. Vacation Payout</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="13" t="inlineStr">
-        <is>
-          <t>For deposit sizing, we use the statutory entitlement from the EA/config — not the T&amp;A system balance (which HR does not trust).</t>
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>Max Cap</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Days</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>Fill if there is a maximum cap we need to adhere to</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>Pay out accrued vacation during termination?</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="inlineStr"/>
-      <c r="C25" s="13" t="inlineStr">
-        <is>
-          <t>Yes / No</t>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>3. Severance Cost Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>Use remaining days on contract as severance?</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>Yes / No — if Yes, skip tier table below</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>5. Compensation Variable Metadata</t>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Component 1: Redundancy Pay OR Termination w/o cause (default)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="13" t="inlineStr">
-        <is>
-          <t>For each compensation variable, indicate Yes/No for each column. New variables default to No.</t>
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>Prorate for partial years?</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>Example: The policy grants 30 days of severance per year. If proration is applied, an employee with 8 months of tenure receives 20 days. If not applied, the employee receives 0 days.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t>Compensation Variable</t>
+          <t>From (tenure months)</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>Included in Working Notice?</t>
+          <t>To (tenure months)</t>
         </is>
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>Included in Severance?</t>
+          <t>Method</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>Included in Vacation Pay?</t>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="inlineStr">
-        <is>
-          <t>Gross Base Salary</t>
-        </is>
-      </c>
-      <c r="B31" s="15" t="inlineStr"/>
-      <c r="C31" s="15" t="inlineStr"/>
-      <c r="D31" s="15" t="inlineStr"/>
+      <c r="A31" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>No Limit</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="inlineStr"/>
+      <c r="A32" s="15" t="inlineStr"/>
       <c r="B32" s="15" t="inlineStr"/>
       <c r="C32" s="15" t="inlineStr"/>
       <c r="D32" s="15" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="inlineStr"/>
+      <c r="A33" s="15" t="inlineStr"/>
       <c r="B33" s="15" t="inlineStr"/>
       <c r="C33" s="15" t="inlineStr"/>
       <c r="D33" s="15" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="11" t="inlineStr"/>
-      <c r="B34" s="15" t="inlineStr"/>
-      <c r="C34" s="15" t="inlineStr"/>
-      <c r="D34" s="15" t="inlineStr"/>
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>↳ Add more tiers by inserting rows above this line</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="11" t="inlineStr"/>
-      <c r="B35" s="15" t="inlineStr"/>
-      <c r="C35" s="15" t="inlineStr"/>
-      <c r="D35" s="15" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="13" t="inlineStr">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>Max Cap</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Days</t>
+        </is>
+      </c>
+      <c r="D35" s="13" t="inlineStr">
+        <is>
+          <t>Fill if there is a maximum cap we need to adhere to</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="13" t="inlineStr">
+        <is>
+          <t>↳ To add another component, copy a component block above and change the label</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>4. Vacation Payout</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>Pay out accrued vacation during termination?</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C41" s="13" t="inlineStr">
+        <is>
+          <t>Yes / No</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>What is the minimum that needs to be paid out?</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>Fixed number of days</t>
+        </is>
+      </c>
+      <c r="C42" s="13" t="inlineStr">
+        <is>
+          <t>Fill the tier table below and max cap if choosing "Fixed Number of Days"; Ignore if it is "All Accrued"</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="14" t="inlineStr">
+        <is>
+          <t>From (tenure months)</t>
+        </is>
+      </c>
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>To (tenure months)</t>
+        </is>
+      </c>
+      <c r="C43" s="14" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="D43" s="14" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="B44" s="15" t="inlineStr">
+        <is>
+          <t>No Limit</t>
+        </is>
+      </c>
+      <c r="C44" s="15" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="D44" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="15" t="inlineStr"/>
+      <c r="B45" s="15" t="inlineStr"/>
+      <c r="C45" s="15" t="inlineStr"/>
+      <c r="D45" s="15" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="15" t="inlineStr"/>
+      <c r="B46" s="15" t="inlineStr"/>
+      <c r="C46" s="15" t="inlineStr"/>
+      <c r="D46" s="15" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="13" t="inlineStr">
+        <is>
+          <t>↳ Add more tiers by inserting rows above this line</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t>Max Cap</t>
+        </is>
+      </c>
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Days</t>
+        </is>
+      </c>
+      <c r="D48" s="13" t="inlineStr">
+        <is>
+          <t>Fill if there is a maximum cap we need to adhere to</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>5. Compensation Variable Metadata</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="14" t="inlineStr">
+        <is>
+          <t>Compensation Variable</t>
+        </is>
+      </c>
+      <c r="B52" s="14" t="inlineStr">
+        <is>
+          <t>Included in Working Notice?</t>
+        </is>
+      </c>
+      <c r="C52" s="14" t="inlineStr">
+        <is>
+          <t>Included in Severance?</t>
+        </is>
+      </c>
+      <c r="D52" s="14" t="inlineStr">
+        <is>
+          <t>Included in Vacation Pay?</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
+          <t>Gross Base Salary</t>
+        </is>
+      </c>
+      <c r="B53" s="15" t="inlineStr"/>
+      <c r="C53" s="15" t="inlineStr"/>
+      <c r="D53" s="15" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="11" t="inlineStr"/>
+      <c r="B54" s="15" t="inlineStr"/>
+      <c r="C54" s="15" t="inlineStr"/>
+      <c r="D54" s="15" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="11" t="inlineStr"/>
+      <c r="B55" s="15" t="inlineStr"/>
+      <c r="C55" s="15" t="inlineStr"/>
+      <c r="D55" s="15" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="11" t="inlineStr"/>
+      <c r="B56" s="15" t="inlineStr"/>
+      <c r="C56" s="15" t="inlineStr"/>
+      <c r="D56" s="15" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="11" t="inlineStr"/>
+      <c r="B57" s="15" t="inlineStr"/>
+      <c r="C57" s="15" t="inlineStr"/>
+      <c r="D57" s="15" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="13" t="inlineStr">
         <is>
           <t>↳ Add more variables by inserting rows above</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
         <is>
           <t>6. Notes / Items Not Captured</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="13" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="13" t="inlineStr">
         <is>
           <t>Use this section to flag anything the config above cannot express:</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">• </t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">• </t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">• </t>
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• </t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <dataValidations count="21">
+  <dataValidations count="31">
     <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
       <formula1>"Indefinite,Fixed Term"</formula1>
     </dataValidation>
-    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
       <formula1>"No,Yes — always,Yes — above tenure threshold"</formula1>
     </dataValidation>
-    <dataValidation sqref="B11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+    <dataValidation sqref="B17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
       <formula1>"Fixed,Per year of service"</formula1>
     </dataValidation>
-    <dataValidation sqref="C14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+    <dataValidation sqref="C20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
       <formula1>"Fixed,Per year of service"</formula1>
     </dataValidation>
-    <dataValidation sqref="B25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+    <dataValidation sqref="C21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Fixed,Per year of service"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
     <dataValidation sqref="C31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
+      <formula1>"Fixed,Per year of service"</formula1>
     </dataValidation>
     <dataValidation sqref="C32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
+      <formula1>"Fixed,Per year of service"</formula1>
     </dataValidation>
     <dataValidation sqref="C33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Fixed,Per year of service"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"All Accrued,Fixed number of days"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Fixed,Per year of service"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Fixed,Per year of service"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Fixed,Per year of service"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B55" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C55" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D55" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" promptTitle="Select" prompt="Choose from the list" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
